--- a/orders.xlsx
+++ b/orders.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="88">
   <si>
     <t>Order ID</t>
   </si>
@@ -254,6 +254,27 @@
   </si>
   <si>
     <t>SF-20260610-6932</t>
+  </si>
+  <si>
+    <t>SF-20260620-3067</t>
+  </si>
+  <si>
+    <t>White Christian Bridal Costume (S) x1</t>
+  </si>
+  <si>
+    <t>20/06/2026</t>
+  </si>
+  <si>
+    <t>SF-20260628-3413</t>
+  </si>
+  <si>
+    <t>Karthik Raja</t>
+  </si>
+  <si>
+    <t>7/149 krishnrajapuram main road</t>
+  </si>
+  <si>
+    <t>28/06/2026</t>
   </si>
 </sst>
 </file>
@@ -649,7 +670,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O13"/>
+  <dimension ref="A1:O15"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
@@ -1276,6 +1297,100 @@
         <v>73</v>
       </c>
     </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>81</v>
+      </c>
+      <c r="B14" t="s">
+        <v>44</v>
+      </c>
+      <c r="C14" t="s">
+        <v>17</v>
+      </c>
+      <c r="D14" t="s">
+        <v>18</v>
+      </c>
+      <c r="E14" t="s">
+        <v>40</v>
+      </c>
+      <c r="F14" t="s">
+        <v>45</v>
+      </c>
+      <c r="G14" t="s">
+        <v>33</v>
+      </c>
+      <c r="H14" t="s">
+        <v>34</v>
+      </c>
+      <c r="I14" t="s">
+        <v>82</v>
+      </c>
+      <c r="J14">
+        <v>100</v>
+      </c>
+      <c r="K14">
+        <v>18</v>
+      </c>
+      <c r="L14">
+        <v>118</v>
+      </c>
+      <c r="M14" t="s">
+        <v>71</v>
+      </c>
+      <c r="N14" t="s">
+        <v>72</v>
+      </c>
+      <c r="O14" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>84</v>
+      </c>
+      <c r="B15" t="s">
+        <v>85</v>
+      </c>
+      <c r="C15" t="s">
+        <v>17</v>
+      </c>
+      <c r="D15" t="s">
+        <v>18</v>
+      </c>
+      <c r="E15" t="s">
+        <v>86</v>
+      </c>
+      <c r="F15" t="s">
+        <v>20</v>
+      </c>
+      <c r="G15" t="s">
+        <v>21</v>
+      </c>
+      <c r="H15" t="s">
+        <v>22</v>
+      </c>
+      <c r="I15" t="s">
+        <v>68</v>
+      </c>
+      <c r="J15">
+        <v>1</v>
+      </c>
+      <c r="K15">
+        <v>0.18</v>
+      </c>
+      <c r="L15">
+        <v>1.18</v>
+      </c>
+      <c r="M15" t="s">
+        <v>55</v>
+      </c>
+      <c r="N15" t="s">
+        <v>25</v>
+      </c>
+      <c r="O15" t="s">
+        <v>87</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
